--- a/cfph_cl.xlsx
+++ b/cfph_cl.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\morex\OneDrive\Desktop\CFPH_Test.sikuli\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Devs\ProjectPOM\Test_Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1053C20A-5C02-4CB6-99DD-49075D7EFED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E79A498-7FBE-4669-8B2A-6BE5F24669EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -72,9 +72,6 @@
     <t>Balloon Hammer</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Blade Knuckles</t>
   </si>
   <si>
@@ -118,6 +115,9 @@
   </si>
   <si>
     <t>Keris Logo</t>
+  </si>
+  <si>
+    <t>N/I</t>
   </si>
 </sst>
 </file>
@@ -257,42 +257,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFEE0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFFC000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <b/>
@@ -331,9 +307,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -371,7 +347,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -477,7 +453,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -619,7 +595,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -628,15 +604,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="3" width="15.83203125" style="4" customWidth="1"/>
-    <col min="4" max="5" width="18.08203125" style="4" customWidth="1"/>
-    <col min="6" max="6" width="69.58203125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="18.25" style="4" customWidth="1"/>
+    <col min="1" max="3" width="15.796875" style="4" customWidth="1"/>
+    <col min="4" max="5" width="18.09765625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="69.59765625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="18.19921875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -649,7 +625,7 @@
       <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
@@ -659,7 +635,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -668,18 +644,18 @@
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <f t="shared" ref="A3:A19" si="0">ROW()-2</f>
         <v>1</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="7" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="2" t="s">
@@ -689,10 +665,10 @@
         <v>11</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -707,10 +683,10 @@
         <v>11</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -719,16 +695,16 @@
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
       <c r="E5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -737,16 +713,16 @@
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -755,16 +731,16 @@
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -773,16 +749,16 @@
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -791,16 +767,16 @@
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -809,16 +785,16 @@
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -827,16 +803,16 @@
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -845,16 +821,16 @@
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -863,16 +839,16 @@
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -881,16 +857,16 @@
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -899,16 +875,16 @@
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -917,16 +893,16 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -935,16 +911,16 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -953,16 +929,16 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -971,27 +947,27 @@
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="B3:B19"/>
     <mergeCell ref="C3:C19"/>
     <mergeCell ref="D3:D19"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A1:A2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3:G19">
